--- a/data/raw/data.xlsx
+++ b/data/raw/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Desktop\ML and Building permits\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wujiabin/dev/dbp/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{4AC029D2-176B-4B80-960D-9967A2FE5E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DB84931-75AC-4122-B2B4-25E612D725D3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC7AAE8-E93E-1F42-85AD-6737F7855B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7423,7 +7423,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7852,41 +7852,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE102"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AC102"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="45.28515625" customWidth="1"/>
-    <col min="2" max="2" width="77.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.42578125" customWidth="1"/>
+    <col min="1" max="1" width="45.33203125" customWidth="1"/>
+    <col min="2" max="2" width="77.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5" customWidth="1"/>
     <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="77.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="159.140625" customWidth="1"/>
-    <col min="8" max="8" width="151.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="77.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="159.1640625" customWidth="1"/>
+    <col min="8" max="8" width="151.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="36" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="22" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.28515625" customWidth="1"/>
-    <col min="26" max="26" width="13.28515625" customWidth="1"/>
+    <col min="20" max="20" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.33203125" customWidth="1"/>
+    <col min="26" max="26" width="13.33203125" customWidth="1"/>
     <col min="27" max="27" width="16" customWidth="1"/>
-    <col min="29" max="29" width="8.140625" customWidth="1"/>
-    <col min="31" max="31" width="26.42578125" customWidth="1"/>
+    <col min="28" max="28" width="12" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="33.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7971,11 +7971,11 @@
       <c r="AB1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AC1" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="4" customFormat="1" ht="169.5" customHeight="1">
+    <row r="2" spans="1:29" s="4" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -8058,13 +8058,11 @@
       <c r="AB2" s="15">
         <v>220039</v>
       </c>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15" t="s">
+      <c r="AC2" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="AE2" s="15"/>
     </row>
-    <row r="3" spans="1:31" s="4" customFormat="1" ht="198" customHeight="1">
+    <row r="3" spans="1:29" s="4" customFormat="1" ht="198" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>46</v>
       </c>
@@ -8147,13 +8145,11 @@
       <c r="AB3" s="15">
         <v>220019</v>
       </c>
-      <c r="AC3" s="15"/>
-      <c r="AD3" s="15" t="s">
+      <c r="AC3" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="AE3" s="15"/>
     </row>
-    <row r="4" spans="1:31" s="4" customFormat="1" ht="202.5" customHeight="1">
+    <row r="4" spans="1:29" s="4" customFormat="1" ht="202.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>46</v>
       </c>
@@ -8233,13 +8229,11 @@
       <c r="AB4" s="15">
         <v>223015</v>
       </c>
-      <c r="AC4" s="15"/>
-      <c r="AD4" s="15" t="s">
+      <c r="AC4" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AE4" s="15"/>
     </row>
-    <row r="5" spans="1:31" s="4" customFormat="1" ht="375">
+    <row r="5" spans="1:29" s="4" customFormat="1" ht="380" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
@@ -8319,13 +8313,11 @@
       <c r="AB5" s="15">
         <v>317023</v>
       </c>
-      <c r="AC5" s="15"/>
-      <c r="AD5" s="15" t="s">
+      <c r="AC5" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="AE5" s="15"/>
     </row>
-    <row r="6" spans="1:31" s="4" customFormat="1" ht="195" customHeight="1">
+    <row r="6" spans="1:29" s="4" customFormat="1" ht="195" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>76</v>
       </c>
@@ -8405,13 +8397,11 @@
       <c r="AB6" s="15">
         <v>515110</v>
       </c>
-      <c r="AC6" s="15"/>
-      <c r="AD6" s="15" t="s">
+      <c r="AC6" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="AE6" s="15"/>
     </row>
-    <row r="7" spans="1:31" s="4" customFormat="1" ht="375" customHeight="1">
+    <row r="7" spans="1:29" s="4" customFormat="1" ht="375" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>89</v>
       </c>
@@ -8491,13 +8481,11 @@
       <c r="AB7" s="15">
         <v>318144</v>
       </c>
-      <c r="AC7" s="15"/>
-      <c r="AD7" s="15" t="s">
+      <c r="AC7" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="AE7" s="15"/>
     </row>
-    <row r="8" spans="1:31" s="4" customFormat="1" ht="171" customHeight="1">
+    <row r="8" spans="1:29" s="4" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>99</v>
       </c>
@@ -8577,13 +8565,11 @@
       <c r="AB8" s="15">
         <v>130050</v>
       </c>
-      <c r="AC8" s="15"/>
-      <c r="AD8" s="15" t="s">
+      <c r="AC8" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="AE8" s="15"/>
     </row>
-    <row r="9" spans="1:31" s="4" customFormat="1" ht="180">
+    <row r="9" spans="1:29" s="4" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>111</v>
       </c>
@@ -8657,13 +8643,11 @@
       <c r="AB9" s="15">
         <v>130152</v>
       </c>
-      <c r="AC9" s="15"/>
-      <c r="AD9" s="15" t="s">
+      <c r="AC9" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="AE9" s="15"/>
     </row>
-    <row r="10" spans="1:31" s="4" customFormat="1" ht="180">
+    <row r="10" spans="1:29" s="4" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>125</v>
       </c>
@@ -8743,13 +8727,11 @@
       <c r="AB10" s="15">
         <v>515066</v>
       </c>
-      <c r="AC10" s="15"/>
-      <c r="AD10" s="15" t="s">
+      <c r="AC10" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="AE10" s="15"/>
     </row>
-    <row r="11" spans="1:31" s="4" customFormat="1" ht="270">
+    <row r="11" spans="1:29" s="4" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>135</v>
       </c>
@@ -8829,13 +8811,11 @@
       <c r="AB11" s="15">
         <v>526224</v>
       </c>
-      <c r="AC11" s="15"/>
-      <c r="AD11" s="15" t="s">
+      <c r="AC11" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="AE11" s="15"/>
     </row>
-    <row r="12" spans="1:31" s="4" customFormat="1" ht="200.25" customHeight="1">
+    <row r="12" spans="1:29" s="4" customFormat="1" ht="200.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>145</v>
       </c>
@@ -8918,13 +8898,11 @@
       <c r="AB12" s="15">
         <v>518010</v>
       </c>
-      <c r="AC12" s="15"/>
-      <c r="AD12" s="15" t="s">
+      <c r="AC12" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="AE12" s="15"/>
     </row>
-    <row r="13" spans="1:31" s="4" customFormat="1" ht="393" customHeight="1">
+    <row r="13" spans="1:29" s="4" customFormat="1" ht="393" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>157</v>
       </c>
@@ -9004,13 +8982,11 @@
       <c r="AB13" s="15">
         <v>525077</v>
       </c>
-      <c r="AC13" s="15"/>
-      <c r="AD13" s="15" t="s">
+      <c r="AC13" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="AE13" s="15"/>
     </row>
-    <row r="14" spans="1:31" s="4" customFormat="1" ht="333.75" customHeight="1">
+    <row r="14" spans="1:29" s="4" customFormat="1" ht="333.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>166</v>
       </c>
@@ -9083,10 +9059,8 @@
       </c>
       <c r="AB14" s="15"/>
       <c r="AC14" s="15"/>
-      <c r="AD14" s="15"/>
-      <c r="AE14" s="15"/>
     </row>
-    <row r="15" spans="1:31" s="4" customFormat="1" ht="195">
+    <row r="15" spans="1:29" s="4" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>175</v>
       </c>
@@ -9164,13 +9138,11 @@
       <c r="AB15" s="15">
         <v>130266</v>
       </c>
-      <c r="AC15" s="15"/>
-      <c r="AD15" s="15" t="s">
+      <c r="AC15" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="AE15" s="15"/>
     </row>
-    <row r="16" spans="1:31" s="4" customFormat="1" ht="315">
+    <row r="16" spans="1:29" s="4" customFormat="1" ht="335" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>185</v>
       </c>
@@ -9250,13 +9222,11 @@
       <c r="AB16" s="15">
         <v>526168</v>
       </c>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="15" t="s">
+      <c r="AC16" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="AE16" s="15"/>
     </row>
-    <row r="17" spans="1:31" s="4" customFormat="1" ht="195">
+    <row r="17" spans="1:29" s="4" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>195</v>
       </c>
@@ -9336,13 +9306,11 @@
       <c r="AB17" s="15">
         <v>130278</v>
       </c>
-      <c r="AC17" s="15"/>
-      <c r="AD17" s="15" t="s">
+      <c r="AC17" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="AE17" s="15"/>
     </row>
-    <row r="18" spans="1:31" s="4" customFormat="1" ht="210" customHeight="1">
+    <row r="18" spans="1:29" s="4" customFormat="1" ht="210" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>202</v>
       </c>
@@ -9422,13 +9390,11 @@
       <c r="AB18" s="15">
         <v>318020</v>
       </c>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="15" t="s">
+      <c r="AC18" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="AE18" s="15"/>
     </row>
-    <row r="19" spans="1:31" s="4" customFormat="1" ht="213.75" customHeight="1">
+    <row r="19" spans="1:29" s="4" customFormat="1" ht="213.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>212</v>
       </c>
@@ -9506,13 +9472,11 @@
       <c r="AB19" s="15">
         <v>320143</v>
       </c>
-      <c r="AC19" s="15"/>
-      <c r="AD19" s="15" t="s">
+      <c r="AC19" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="AE19" s="15"/>
     </row>
-    <row r="20" spans="1:31" s="4" customFormat="1" ht="200.25" customHeight="1">
+    <row r="20" spans="1:29" s="4" customFormat="1" ht="200.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>221</v>
       </c>
@@ -9592,13 +9556,11 @@
       <c r="AB20" s="15">
         <v>136034</v>
       </c>
-      <c r="AC20" s="15"/>
-      <c r="AD20" s="15" t="s">
+      <c r="AC20" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="AE20" s="15"/>
     </row>
-    <row r="21" spans="1:31" s="4" customFormat="1" ht="207.75" customHeight="1">
+    <row r="21" spans="1:29" s="4" customFormat="1" ht="207.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>233</v>
       </c>
@@ -9678,13 +9640,11 @@
       <c r="AB21" s="15">
         <v>526033</v>
       </c>
-      <c r="AC21" s="15"/>
-      <c r="AD21" s="15" t="s">
+      <c r="AC21" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="AE21" s="15"/>
     </row>
-    <row r="22" spans="1:31" s="4" customFormat="1" ht="195">
+    <row r="22" spans="1:29" s="4" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>242</v>
       </c>
@@ -9762,13 +9722,11 @@
       <c r="AB22" s="15">
         <v>523025</v>
       </c>
-      <c r="AC22" s="15"/>
-      <c r="AD22" s="15" t="s">
+      <c r="AC22" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="AE22" s="15"/>
     </row>
-    <row r="23" spans="1:31" s="4" customFormat="1" ht="408.75" customHeight="1">
+    <row r="23" spans="1:29" s="4" customFormat="1" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>252</v>
       </c>
@@ -9846,13 +9804,11 @@
       <c r="AB23" s="15">
         <v>318075</v>
       </c>
-      <c r="AC23" s="15"/>
-      <c r="AD23" s="15" t="s">
+      <c r="AC23" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="AE23" s="15"/>
     </row>
-    <row r="24" spans="1:31" s="4" customFormat="1" ht="270">
+    <row r="24" spans="1:29" s="4" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>261</v>
       </c>
@@ -9932,13 +9888,11 @@
       <c r="AB24" s="15">
         <v>219068</v>
       </c>
-      <c r="AC24" s="15"/>
-      <c r="AD24" s="15" t="s">
+      <c r="AC24" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="AE24" s="15"/>
     </row>
-    <row r="25" spans="1:31" s="4" customFormat="1" ht="225">
+    <row r="25" spans="1:29" s="4" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>270</v>
       </c>
@@ -10018,13 +9972,11 @@
       <c r="AB25" s="15">
         <v>227116</v>
       </c>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15" t="s">
+      <c r="AC25" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="AE25" s="15"/>
     </row>
-    <row r="26" spans="1:31" s="4" customFormat="1" ht="405">
+    <row r="26" spans="1:29" s="4" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>279</v>
       </c>
@@ -10102,13 +10054,11 @@
       <c r="AB26" s="15">
         <v>514074</v>
       </c>
-      <c r="AC26" s="15"/>
-      <c r="AD26" s="15" t="s">
+      <c r="AC26" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="AE26" s="15"/>
     </row>
-    <row r="27" spans="1:31" s="4" customFormat="1" ht="200.25" customHeight="1">
+    <row r="27" spans="1:29" s="4" customFormat="1" ht="200.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>287</v>
       </c>
@@ -10188,13 +10138,11 @@
       <c r="AB27" s="15">
         <v>607019</v>
       </c>
-      <c r="AC27" s="15"/>
-      <c r="AD27" s="15" t="s">
+      <c r="AC27" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="AE27" s="15"/>
     </row>
-    <row r="28" spans="1:31" s="4" customFormat="1" ht="195">
+    <row r="28" spans="1:29" s="4" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>300</v>
       </c>
@@ -10277,13 +10225,11 @@
       <c r="AB28" s="15">
         <v>515084</v>
       </c>
-      <c r="AC28" s="15"/>
-      <c r="AD28" s="15" t="s">
+      <c r="AC28" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="AE28" s="15"/>
     </row>
-    <row r="29" spans="1:31" s="4" customFormat="1" ht="206.25" customHeight="1">
+    <row r="29" spans="1:29" s="4" customFormat="1" ht="206.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>308</v>
       </c>
@@ -10363,13 +10309,11 @@
       <c r="AB29" s="15">
         <v>518022</v>
       </c>
-      <c r="AC29" s="15"/>
-      <c r="AD29" s="15" t="s">
+      <c r="AC29" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="AE29" s="15"/>
     </row>
-    <row r="30" spans="1:31" s="4" customFormat="1" ht="210" customHeight="1">
+    <row r="30" spans="1:29" s="4" customFormat="1" ht="210" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>318</v>
       </c>
@@ -10454,13 +10398,11 @@
       <c r="AB30" s="15">
         <v>517080</v>
       </c>
-      <c r="AC30" s="15"/>
-      <c r="AD30" s="15" t="s">
+      <c r="AC30" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="AE30" s="15"/>
     </row>
-    <row r="31" spans="1:31" s="4" customFormat="1" ht="210" customHeight="1">
+    <row r="31" spans="1:29" s="4" customFormat="1" ht="210" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>329</v>
       </c>
@@ -10540,13 +10482,11 @@
       <c r="AB31" s="15">
         <v>514069</v>
       </c>
-      <c r="AC31" s="15"/>
-      <c r="AD31" s="15" t="s">
+      <c r="AC31" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="AE31" s="15"/>
     </row>
-    <row r="32" spans="1:31" s="4" customFormat="1" ht="191.25" customHeight="1">
+    <row r="32" spans="1:29" s="4" customFormat="1" ht="191.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>337</v>
       </c>
@@ -10628,13 +10568,11 @@
       <c r="AB32" s="15">
         <v>519081</v>
       </c>
-      <c r="AC32" s="15"/>
-      <c r="AD32" s="15" t="s">
+      <c r="AC32" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="AE32" s="15"/>
     </row>
-    <row r="33" spans="1:31" s="4" customFormat="1" ht="180">
+    <row r="33" spans="1:29" s="4" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>348</v>
       </c>
@@ -10714,13 +10652,11 @@
       <c r="AB33" s="15">
         <v>513007</v>
       </c>
-      <c r="AC33" s="15"/>
-      <c r="AD33" s="15" t="s">
+      <c r="AC33" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="AE33" s="15"/>
     </row>
-    <row r="34" spans="1:31" s="4" customFormat="1" ht="219" customHeight="1">
+    <row r="34" spans="1:29" s="4" customFormat="1" ht="219" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>359</v>
       </c>
@@ -10800,13 +10736,11 @@
       <c r="AB34" s="15">
         <v>515100</v>
       </c>
-      <c r="AC34" s="15"/>
-      <c r="AD34" s="15" t="s">
+      <c r="AC34" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="AE34" s="15"/>
     </row>
-    <row r="35" spans="1:31" s="4" customFormat="1" ht="258.75" customHeight="1">
+    <row r="35" spans="1:29" s="4" customFormat="1" ht="258.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>366</v>
       </c>
@@ -10886,13 +10820,11 @@
       <c r="AB35" s="15">
         <v>318139</v>
       </c>
-      <c r="AC35" s="15"/>
-      <c r="AD35" s="15" t="s">
+      <c r="AC35" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="AE35" s="15"/>
     </row>
-    <row r="36" spans="1:31" s="4" customFormat="1" ht="330">
+    <row r="36" spans="1:29" s="4" customFormat="1" ht="350" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>374</v>
       </c>
@@ -10972,13 +10904,11 @@
       <c r="AB36" s="15">
         <v>220012</v>
       </c>
-      <c r="AC36" s="15"/>
-      <c r="AD36" s="15" t="s">
+      <c r="AC36" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="AE36" s="15"/>
     </row>
-    <row r="37" spans="1:31" s="4" customFormat="1" ht="270">
+    <row r="37" spans="1:29" s="4" customFormat="1" ht="272" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>383</v>
       </c>
@@ -11061,13 +10991,11 @@
       <c r="AB37" s="15">
         <v>601128</v>
       </c>
-      <c r="AC37" s="15"/>
-      <c r="AD37" s="15" t="s">
+      <c r="AC37" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="AE37" s="15"/>
     </row>
-    <row r="38" spans="1:31" s="4" customFormat="1" ht="210" customHeight="1">
+    <row r="38" spans="1:29" s="4" customFormat="1" ht="210" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>395</v>
       </c>
@@ -11149,13 +11077,11 @@
       <c r="AB38" s="15">
         <v>318145</v>
       </c>
-      <c r="AC38" s="15"/>
-      <c r="AD38" s="15" t="s">
+      <c r="AC38" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="AE38" s="15"/>
     </row>
-    <row r="39" spans="1:31" s="4" customFormat="1" ht="272.25" customHeight="1">
+    <row r="39" spans="1:29" s="4" customFormat="1" ht="272.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>405</v>
       </c>
@@ -11237,13 +11163,11 @@
       <c r="AB39" s="15">
         <v>512006</v>
       </c>
-      <c r="AC39" s="15"/>
-      <c r="AD39" s="15" t="s">
+      <c r="AC39" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="AE39" s="15"/>
     </row>
-    <row r="40" spans="1:31" s="4" customFormat="1" ht="213">
+    <row r="40" spans="1:29" s="4" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>418</v>
       </c>
@@ -11325,13 +11249,11 @@
       <c r="AB40" s="15">
         <v>319126</v>
       </c>
-      <c r="AC40" s="15"/>
-      <c r="AD40" s="15" t="s">
+      <c r="AC40" s="15" t="s">
         <v>428</v>
       </c>
-      <c r="AE40" s="15"/>
     </row>
-    <row r="41" spans="1:31" s="4" customFormat="1" ht="229.5">
+    <row r="41" spans="1:29" s="4" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>429</v>
       </c>
@@ -11413,13 +11335,11 @@
       <c r="AB41" s="15">
         <v>525097</v>
       </c>
-      <c r="AC41" s="15"/>
-      <c r="AD41" s="15" t="s">
+      <c r="AC41" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="AE41" s="15"/>
     </row>
-    <row r="42" spans="1:31" s="4" customFormat="1" ht="180">
+    <row r="42" spans="1:29" s="4" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>437</v>
       </c>
@@ -11499,13 +11419,11 @@
       <c r="AB42" s="15">
         <v>141064</v>
       </c>
-      <c r="AC42" s="15"/>
-      <c r="AD42" s="15" t="s">
+      <c r="AC42" s="15" t="s">
         <v>446</v>
       </c>
-      <c r="AE42" s="15"/>
     </row>
-    <row r="43" spans="1:31" s="4" customFormat="1" ht="195">
+    <row r="43" spans="1:29" s="4" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>447</v>
       </c>
@@ -11588,13 +11506,11 @@
       <c r="AB43" s="15">
         <v>601128</v>
       </c>
-      <c r="AC43" s="15"/>
-      <c r="AD43" s="15" t="s">
+      <c r="AC43" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="AE43" s="15"/>
     </row>
-    <row r="44" spans="1:31" s="4" customFormat="1" ht="240">
+    <row r="44" spans="1:29" s="4" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>405</v>
       </c>
@@ -11679,13 +11595,11 @@
       <c r="AB44" s="15">
         <v>512037</v>
       </c>
-      <c r="AC44" s="15"/>
-      <c r="AD44" s="15" t="s">
+      <c r="AC44" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="AE44" s="15"/>
     </row>
-    <row r="45" spans="1:31" s="4" customFormat="1" ht="210">
+    <row r="45" spans="1:29" s="4" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>467</v>
       </c>
@@ -11767,13 +11681,11 @@
       <c r="AB45" s="15">
         <v>520042</v>
       </c>
-      <c r="AC45" s="15"/>
-      <c r="AD45" s="15" t="s">
+      <c r="AC45" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="AE45" s="15"/>
     </row>
-    <row r="46" spans="1:31" s="4" customFormat="1" ht="409.5" customHeight="1">
+    <row r="46" spans="1:29" s="4" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>478</v>
       </c>
@@ -11855,13 +11767,11 @@
       <c r="AB46" s="15">
         <v>432123</v>
       </c>
-      <c r="AC46" s="15"/>
-      <c r="AD46" s="15" t="s">
+      <c r="AC46" s="15" t="s">
         <v>491</v>
       </c>
-      <c r="AE46" s="15"/>
     </row>
-    <row r="47" spans="1:31" s="4" customFormat="1" ht="195">
+    <row r="47" spans="1:29" s="4" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>447</v>
       </c>
@@ -11941,13 +11851,11 @@
       <c r="AB47" s="15">
         <v>319098</v>
       </c>
-      <c r="AC47" s="15"/>
-      <c r="AD47" s="15" t="s">
+      <c r="AC47" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="AE47" s="15"/>
     </row>
-    <row r="48" spans="1:31" s="4" customFormat="1" ht="285">
+    <row r="48" spans="1:29" s="4" customFormat="1" ht="365" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>499</v>
       </c>
@@ -12029,13 +11937,11 @@
       <c r="AB48" s="15">
         <v>521034</v>
       </c>
-      <c r="AC48" s="15"/>
-      <c r="AD48" s="15" t="s">
+      <c r="AC48" s="15" t="s">
         <v>510</v>
       </c>
-      <c r="AE48" s="15"/>
     </row>
-    <row r="49" spans="1:31" s="4" customFormat="1" ht="210">
+    <row r="49" spans="1:29" s="4" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>511</v>
       </c>
@@ -12117,13 +12023,11 @@
       <c r="AB49" s="15">
         <v>520036</v>
       </c>
-      <c r="AC49" s="15"/>
-      <c r="AD49" s="15" t="s">
+      <c r="AC49" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="AE49" s="15"/>
     </row>
-    <row r="50" spans="1:31" s="4" customFormat="1" ht="285">
+    <row r="50" spans="1:29" s="4" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>521</v>
       </c>
@@ -12208,13 +12112,11 @@
       <c r="AB50" s="15">
         <v>220045</v>
       </c>
-      <c r="AC50" s="15"/>
-      <c r="AD50" s="15" t="s">
+      <c r="AC50" s="15" t="s">
         <v>530</v>
       </c>
-      <c r="AE50" s="15"/>
     </row>
-    <row r="51" spans="1:31" s="7" customFormat="1" ht="165">
+    <row r="51" spans="1:29" s="7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>531</v>
       </c>
@@ -12299,13 +12201,11 @@
       <c r="AB51" s="15">
         <v>319060</v>
       </c>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="15" t="s">
+      <c r="AC51" s="15" t="s">
         <v>541</v>
       </c>
-      <c r="AE51" s="15"/>
     </row>
-    <row r="52" spans="1:31" s="7" customFormat="1" ht="165">
+    <row r="52" spans="1:29" s="7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>542</v>
       </c>
@@ -12387,13 +12287,11 @@
       <c r="AB52" s="15">
         <v>517069</v>
       </c>
-      <c r="AC52" s="15"/>
-      <c r="AD52" s="15" t="s">
+      <c r="AC52" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="AE52" s="15"/>
     </row>
-    <row r="53" spans="1:31" s="7" customFormat="1" ht="195">
+    <row r="53" spans="1:29" s="7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>552</v>
       </c>
@@ -12475,13 +12373,11 @@
       <c r="AB53" s="15">
         <v>521005</v>
       </c>
-      <c r="AC53" s="15"/>
-      <c r="AD53" s="15" t="s">
+      <c r="AC53" s="15" t="s">
         <v>561</v>
       </c>
-      <c r="AE53" s="15"/>
     </row>
-    <row r="54" spans="1:31" s="7" customFormat="1" ht="180">
+    <row r="54" spans="1:29" s="7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>562</v>
       </c>
@@ -12563,13 +12459,11 @@
       <c r="AB54" s="15" t="s">
         <v>575</v>
       </c>
-      <c r="AC54" s="15"/>
-      <c r="AD54" s="15" t="s">
+      <c r="AC54" s="15" t="s">
         <v>576</v>
       </c>
-      <c r="AE54" s="15"/>
     </row>
-    <row r="55" spans="1:31" s="7" customFormat="1" ht="375">
+    <row r="55" spans="1:29" s="7" customFormat="1" ht="335" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>577</v>
       </c>
@@ -12651,13 +12545,11 @@
       <c r="AB55" s="15">
         <v>520010</v>
       </c>
-      <c r="AC55" s="15"/>
-      <c r="AD55" s="15" t="s">
+      <c r="AC55" s="15" t="s">
         <v>586</v>
       </c>
-      <c r="AE55" s="15"/>
     </row>
-    <row r="56" spans="1:31" s="7" customFormat="1" ht="409.5">
+    <row r="56" spans="1:29" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>587</v>
       </c>
@@ -12742,13 +12634,11 @@
       <c r="AB56" s="15">
         <v>523044</v>
       </c>
-      <c r="AC56" s="15"/>
-      <c r="AD56" s="15" t="s">
+      <c r="AC56" s="15" t="s">
         <v>599</v>
       </c>
-      <c r="AE56" s="15"/>
     </row>
-    <row r="57" spans="1:31" s="7" customFormat="1" ht="210">
+    <row r="57" spans="1:29" s="7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>600</v>
       </c>
@@ -12830,13 +12720,11 @@
       <c r="AB57" s="15">
         <v>130021</v>
       </c>
-      <c r="AC57" s="15"/>
-      <c r="AD57" s="15" t="s">
+      <c r="AC57" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="AE57" s="15"/>
     </row>
-    <row r="58" spans="1:31" s="7" customFormat="1" ht="330">
+    <row r="58" spans="1:29" s="7" customFormat="1" ht="350" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>610</v>
       </c>
@@ -12921,13 +12809,11 @@
       <c r="AB58" s="15">
         <v>220030</v>
       </c>
-      <c r="AC58" s="15"/>
-      <c r="AD58" s="15" t="s">
+      <c r="AC58" s="15" t="s">
         <v>620</v>
       </c>
-      <c r="AE58" s="15"/>
     </row>
-    <row r="59" spans="1:31" s="7" customFormat="1" ht="255">
+    <row r="59" spans="1:29" s="7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>621</v>
       </c>
@@ -13009,13 +12895,11 @@
       <c r="AB59" s="15">
         <v>136118</v>
       </c>
-      <c r="AC59" s="15"/>
-      <c r="AD59" s="15" t="s">
+      <c r="AC59" s="15" t="s">
         <v>629</v>
       </c>
-      <c r="AE59" s="15"/>
     </row>
-    <row r="60" spans="1:31" s="7" customFormat="1" ht="180">
+    <row r="60" spans="1:29" s="7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>630</v>
       </c>
@@ -13097,13 +12981,11 @@
       <c r="AB60" s="15">
         <v>518021</v>
       </c>
-      <c r="AC60" s="15"/>
-      <c r="AD60" s="15" t="s">
+      <c r="AC60" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="AE60" s="15"/>
     </row>
-    <row r="61" spans="1:31" s="7" customFormat="1" ht="195">
+    <row r="61" spans="1:29" s="7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>640</v>
       </c>
@@ -13176,10 +13058,8 @@
       </c>
       <c r="AB61" s="15"/>
       <c r="AC61" s="15"/>
-      <c r="AD61" s="15"/>
-      <c r="AE61" s="15"/>
     </row>
-    <row r="62" spans="1:31" s="7" customFormat="1" ht="210">
+    <row r="62" spans="1:29" s="7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>646</v>
       </c>
@@ -13261,13 +13141,11 @@
       <c r="AB62" s="15">
         <v>130152</v>
       </c>
-      <c r="AC62" s="15"/>
-      <c r="AD62" s="15" t="s">
+      <c r="AC62" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="AE62" s="15"/>
     </row>
-    <row r="63" spans="1:31" s="7" customFormat="1" ht="240">
+    <row r="63" spans="1:29" s="7" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>655</v>
       </c>
@@ -13352,13 +13230,11 @@
       <c r="AB63" s="15">
         <v>319002</v>
       </c>
-      <c r="AC63" s="15"/>
-      <c r="AD63" s="15" t="s">
+      <c r="AC63" s="15" t="s">
         <v>665</v>
       </c>
-      <c r="AE63" s="15"/>
     </row>
-    <row r="64" spans="1:31" s="7" customFormat="1" ht="270">
+    <row r="64" spans="1:29" s="7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>666</v>
       </c>
@@ -13440,13 +13316,11 @@
       <c r="AB64" s="15">
         <v>526191</v>
       </c>
-      <c r="AC64" s="15"/>
-      <c r="AD64" s="15" t="s">
+      <c r="AC64" s="15" t="s">
         <v>676</v>
       </c>
-      <c r="AE64" s="15"/>
     </row>
-    <row r="65" spans="1:31" s="7" customFormat="1" ht="270">
+    <row r="65" spans="1:29" s="7" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>677</v>
       </c>
@@ -13528,13 +13402,11 @@
       <c r="AB65" s="15">
         <v>510004</v>
       </c>
-      <c r="AC65" s="15"/>
-      <c r="AD65" s="15" t="s">
+      <c r="AC65" s="15" t="s">
         <v>688</v>
       </c>
-      <c r="AE65" s="15"/>
     </row>
-    <row r="66" spans="1:31" s="7" customFormat="1" ht="195">
+    <row r="66" spans="1:29" s="7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>689</v>
       </c>
@@ -13619,13 +13491,11 @@
       <c r="AB66" s="15">
         <v>521005</v>
       </c>
-      <c r="AC66" s="15"/>
-      <c r="AD66" s="15" t="s">
+      <c r="AC66" s="15" t="s">
         <v>561</v>
       </c>
-      <c r="AE66" s="15"/>
     </row>
-    <row r="67" spans="1:31" s="7" customFormat="1" ht="285">
+    <row r="67" spans="1:29" s="7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>700</v>
       </c>
@@ -13707,13 +13577,11 @@
       <c r="AB67" s="15">
         <v>523052</v>
       </c>
-      <c r="AC67" s="15"/>
-      <c r="AD67" s="15" t="s">
+      <c r="AC67" s="15" t="s">
         <v>599</v>
       </c>
-      <c r="AE67" s="15"/>
     </row>
-    <row r="68" spans="1:31" s="7" customFormat="1" ht="405">
+    <row r="68" spans="1:29" s="7" customFormat="1" ht="380" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>709</v>
       </c>
@@ -13795,13 +13663,11 @@
       <c r="AB68" s="15">
         <v>521008</v>
       </c>
-      <c r="AC68" s="15"/>
-      <c r="AD68" s="15" t="s">
+      <c r="AC68" s="15" t="s">
         <v>510</v>
       </c>
-      <c r="AE68" s="15"/>
     </row>
-    <row r="69" spans="1:31" s="7" customFormat="1" ht="409.5">
+    <row r="69" spans="1:29" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>721</v>
       </c>
@@ -13883,13 +13749,11 @@
       <c r="AB69" s="15">
         <v>526001</v>
       </c>
-      <c r="AC69" s="15"/>
-      <c r="AD69" s="15" t="s">
+      <c r="AC69" s="15" t="s">
         <v>730</v>
       </c>
-      <c r="AE69" s="15"/>
     </row>
-    <row r="70" spans="1:31" s="7" customFormat="1" ht="240">
+    <row r="70" spans="1:29" s="7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>731</v>
       </c>
@@ -13971,13 +13835,11 @@
       <c r="AB70" s="15">
         <v>130050</v>
       </c>
-      <c r="AC70" s="15"/>
-      <c r="AD70" s="15" t="s">
+      <c r="AC70" s="15" t="s">
         <v>741</v>
       </c>
-      <c r="AE70" s="15"/>
     </row>
-    <row r="71" spans="1:31" s="7" customFormat="1" ht="409.5">
+    <row r="71" spans="1:29" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>742</v>
       </c>
@@ -14062,13 +13924,11 @@
       <c r="AB71" s="15">
         <v>227125</v>
       </c>
-      <c r="AC71" s="15"/>
-      <c r="AD71" s="15" t="s">
+      <c r="AC71" s="15" t="s">
         <v>752</v>
       </c>
-      <c r="AE71" s="15"/>
     </row>
-    <row r="72" spans="1:31" s="7" customFormat="1" ht="345">
+    <row r="72" spans="1:29" s="7" customFormat="1" ht="365" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>753</v>
       </c>
@@ -14150,13 +14010,11 @@
       <c r="AB72" s="15">
         <v>518012</v>
       </c>
-      <c r="AC72" s="15"/>
-      <c r="AD72" s="15" t="s">
+      <c r="AC72" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="AE72" s="15"/>
     </row>
-    <row r="73" spans="1:31" s="7" customFormat="1" ht="409.5">
+    <row r="73" spans="1:29" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>765</v>
       </c>
@@ -14241,13 +14099,11 @@
       <c r="AB73" s="15">
         <v>219040</v>
       </c>
-      <c r="AC73" s="15"/>
-      <c r="AD73" s="15" t="s">
+      <c r="AC73" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="AE73" s="15"/>
     </row>
-    <row r="74" spans="1:31" s="6" customFormat="1" ht="409.5">
+    <row r="74" spans="1:29" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>577</v>
       </c>
@@ -14329,13 +14185,11 @@
       <c r="AB74" s="15">
         <v>520010</v>
       </c>
-      <c r="AC74" s="15"/>
-      <c r="AD74" s="15" t="s">
+      <c r="AC74" s="15" t="s">
         <v>586</v>
       </c>
-      <c r="AE74" s="15"/>
     </row>
-    <row r="75" spans="1:31" s="7" customFormat="1" ht="360">
+    <row r="75" spans="1:29" s="7" customFormat="1" ht="365" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>782</v>
       </c>
@@ -14417,13 +14271,11 @@
       <c r="AB75" s="15">
         <v>521005</v>
       </c>
-      <c r="AC75" s="15"/>
-      <c r="AD75" s="15" t="s">
+      <c r="AC75" s="15" t="s">
         <v>561</v>
       </c>
-      <c r="AE75" s="15"/>
     </row>
-    <row r="76" spans="1:31" s="7" customFormat="1" ht="210">
+    <row r="76" spans="1:29" s="7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>791</v>
       </c>
@@ -14508,13 +14360,11 @@
       <c r="AB76" s="15">
         <v>515068</v>
       </c>
-      <c r="AC76" s="15"/>
-      <c r="AD76" s="15" t="s">
+      <c r="AC76" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="AE76" s="15"/>
     </row>
-    <row r="77" spans="1:31" s="7" customFormat="1" ht="409.5">
+    <row r="77" spans="1:29" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>587</v>
       </c>
@@ -14599,13 +14449,11 @@
       <c r="AB77" s="15">
         <v>523044</v>
       </c>
-      <c r="AC77" s="15"/>
-      <c r="AD77" s="15" t="s">
+      <c r="AC77" s="15" t="s">
         <v>599</v>
       </c>
-      <c r="AE77" s="15"/>
     </row>
-    <row r="78" spans="1:31" s="7" customFormat="1" ht="409.5">
+    <row r="78" spans="1:29" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>808</v>
       </c>
@@ -14687,13 +14535,11 @@
       <c r="AB78" s="15">
         <v>223015</v>
       </c>
-      <c r="AC78" s="15"/>
-      <c r="AD78" s="15" t="s">
+      <c r="AC78" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AE78" s="15"/>
     </row>
-    <row r="79" spans="1:31" s="7" customFormat="1" ht="180">
+    <row r="79" spans="1:29" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>817</v>
       </c>
@@ -14775,13 +14621,11 @@
       <c r="AB79" s="15">
         <v>408010</v>
       </c>
-      <c r="AC79" s="15"/>
-      <c r="AD79" s="15" t="s">
+      <c r="AC79" s="15" t="s">
         <v>830</v>
       </c>
-      <c r="AE79" s="15"/>
     </row>
-    <row r="80" spans="1:31" s="7" customFormat="1" ht="405">
+    <row r="80" spans="1:29" s="7" customFormat="1" ht="395" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>831</v>
       </c>
@@ -14863,13 +14707,11 @@
       <c r="AB80" s="15">
         <v>219088</v>
       </c>
-      <c r="AC80" s="15"/>
-      <c r="AD80" s="15" t="s">
+      <c r="AC80" s="15" t="s">
         <v>841</v>
       </c>
-      <c r="AE80" s="15"/>
     </row>
-    <row r="81" spans="1:31" s="7" customFormat="1" ht="165">
+    <row r="81" spans="1:29" s="7" customFormat="1" ht="320" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>842</v>
       </c>
@@ -14954,13 +14796,11 @@
       <c r="AB81" s="15">
         <v>526049</v>
       </c>
-      <c r="AC81" s="15"/>
-      <c r="AD81" s="15" t="s">
+      <c r="AC81" s="15" t="s">
         <v>852</v>
       </c>
-      <c r="AE81" s="15"/>
     </row>
-    <row r="82" spans="1:31" s="7" customFormat="1" ht="210">
+    <row r="82" spans="1:29" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>853</v>
       </c>
@@ -15042,13 +14882,11 @@
       <c r="AB82" s="15" t="s">
         <v>860</v>
       </c>
-      <c r="AC82" s="15"/>
-      <c r="AD82" s="15" t="s">
+      <c r="AC82" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="AE82" s="15"/>
     </row>
-    <row r="83" spans="1:31" s="7" customFormat="1" ht="285">
+    <row r="83" spans="1:29" s="7" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>861</v>
       </c>
@@ -15133,13 +14971,11 @@
       <c r="AB83" s="15">
         <v>321015</v>
       </c>
-      <c r="AC83" s="15"/>
-      <c r="AD83" s="15" t="s">
+      <c r="AC83" s="15" t="s">
         <v>873</v>
       </c>
-      <c r="AE83" s="15"/>
     </row>
-    <row r="84" spans="1:31" s="7" customFormat="1" ht="180">
+    <row r="84" spans="1:29" s="7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>874</v>
       </c>
@@ -15221,13 +15057,11 @@
       <c r="AB84" s="15">
         <v>130266</v>
       </c>
-      <c r="AC84" s="15"/>
-      <c r="AD84" s="15" t="s">
+      <c r="AC84" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="AE84" s="15"/>
     </row>
-    <row r="85" spans="1:31" s="7" customFormat="1" ht="165">
+    <row r="85" spans="1:29" s="7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>880</v>
       </c>
@@ -15309,13 +15143,11 @@
       <c r="AB85" s="15">
         <v>523056</v>
       </c>
-      <c r="AC85" s="15"/>
-      <c r="AD85" s="15" t="s">
+      <c r="AC85" s="15" t="s">
         <v>599</v>
       </c>
-      <c r="AE85" s="15"/>
     </row>
-    <row r="86" spans="1:31" s="7" customFormat="1" ht="195">
+    <row r="86" spans="1:29" s="7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>890</v>
       </c>
@@ -15397,13 +15229,11 @@
       <c r="AB86" s="15">
         <v>130189</v>
       </c>
-      <c r="AC86" s="15"/>
-      <c r="AD86" s="15" t="s">
+      <c r="AC86" s="15" t="s">
         <v>899</v>
       </c>
-      <c r="AE86" s="15"/>
     </row>
-    <row r="87" spans="1:31" s="7" customFormat="1" ht="195">
+    <row r="87" spans="1:29" s="7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>900</v>
       </c>
@@ -15488,13 +15318,11 @@
       <c r="AB87" s="15">
         <v>604007</v>
       </c>
-      <c r="AC87" s="15"/>
-      <c r="AD87" s="15" t="s">
+      <c r="AC87" s="15" t="s">
         <v>913</v>
       </c>
-      <c r="AE87" s="15"/>
     </row>
-    <row r="88" spans="1:31" s="7" customFormat="1" ht="210">
+    <row r="88" spans="1:29" s="7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>914</v>
       </c>
@@ -15576,13 +15404,11 @@
       <c r="AB88" s="15">
         <v>130266</v>
       </c>
-      <c r="AC88" s="15"/>
-      <c r="AD88" s="15" t="s">
+      <c r="AC88" s="15" t="s">
         <v>922</v>
       </c>
-      <c r="AE88" s="15"/>
     </row>
-    <row r="89" spans="1:31" s="7" customFormat="1" ht="180">
+    <row r="89" spans="1:29" s="7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>923</v>
       </c>
@@ -15664,13 +15490,11 @@
       <c r="AB89" s="15">
         <v>130152</v>
       </c>
-      <c r="AC89" s="15"/>
-      <c r="AD89" s="15" t="s">
+      <c r="AC89" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="AE89" s="15"/>
     </row>
-    <row r="90" spans="1:31" s="7" customFormat="1" ht="165">
+    <row r="90" spans="1:29" s="7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>931</v>
       </c>
@@ -15752,13 +15576,11 @@
       <c r="AB90" s="15">
         <v>318104</v>
       </c>
-      <c r="AC90" s="15"/>
-      <c r="AD90" s="15" t="s">
+      <c r="AC90" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="AE90" s="15"/>
     </row>
-    <row r="91" spans="1:31" s="7" customFormat="1" ht="165">
+    <row r="91" spans="1:29" s="7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>941</v>
       </c>
@@ -15840,13 +15662,11 @@
       <c r="AB91" s="15">
         <v>130267</v>
       </c>
-      <c r="AC91" s="15"/>
-      <c r="AD91" s="15" t="s">
+      <c r="AC91" s="15" t="s">
         <v>922</v>
       </c>
-      <c r="AE91" s="15"/>
     </row>
-    <row r="92" spans="1:31" s="7" customFormat="1" ht="195">
+    <row r="92" spans="1:29" s="7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>950</v>
       </c>
@@ -15928,13 +15748,11 @@
       <c r="AB92" s="15">
         <v>525051</v>
       </c>
-      <c r="AC92" s="15"/>
-      <c r="AD92" s="15" t="s">
+      <c r="AC92" s="15" t="s">
         <v>960</v>
       </c>
-      <c r="AE92" s="15"/>
     </row>
-    <row r="93" spans="1:31" s="7" customFormat="1" ht="210">
+    <row r="93" spans="1:29" s="7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>961</v>
       </c>
@@ -16019,13 +15837,11 @@
       <c r="AB93" s="15">
         <v>523073</v>
       </c>
-      <c r="AC93" s="15"/>
-      <c r="AD93" s="15" t="s">
+      <c r="AC93" s="15" t="s">
         <v>970</v>
       </c>
-      <c r="AE93" s="15"/>
     </row>
-    <row r="94" spans="1:31" s="7" customFormat="1" ht="375">
+    <row r="94" spans="1:29" s="7" customFormat="1" ht="365" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>971</v>
       </c>
@@ -16107,13 +15923,11 @@
       <c r="AB94" s="15">
         <v>607045</v>
       </c>
-      <c r="AC94" s="15"/>
-      <c r="AD94" s="15" t="s">
+      <c r="AC94" s="15" t="s">
         <v>446</v>
       </c>
-      <c r="AE94" s="15"/>
     </row>
-    <row r="95" spans="1:31" s="7" customFormat="1" ht="165">
+    <row r="95" spans="1:29" s="7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>978</v>
       </c>
@@ -16188,10 +16002,8 @@
       </c>
       <c r="AB95" s="15"/>
       <c r="AC95" s="15"/>
-      <c r="AD95" s="15"/>
-      <c r="AE95" s="15"/>
     </row>
-    <row r="96" spans="1:31" s="7" customFormat="1" ht="165">
+    <row r="96" spans="1:29" s="7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>987</v>
       </c>
@@ -16273,13 +16085,11 @@
       <c r="AB96" s="15">
         <v>130267</v>
       </c>
-      <c r="AC96" s="15"/>
-      <c r="AD96" s="15" t="s">
+      <c r="AC96" s="15" t="s">
         <v>922</v>
       </c>
-      <c r="AE96" s="15"/>
     </row>
-    <row r="97" spans="1:31" s="7" customFormat="1" ht="270">
+    <row r="97" spans="1:29" s="7" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>731</v>
       </c>
@@ -16361,13 +16171,11 @@
       <c r="AB97" s="15">
         <v>130050</v>
       </c>
-      <c r="AC97" s="15"/>
-      <c r="AD97" s="15" t="s">
+      <c r="AC97" s="15" t="s">
         <v>741</v>
       </c>
-      <c r="AE97" s="15"/>
     </row>
-    <row r="98" spans="1:31" s="7" customFormat="1" ht="360">
+    <row r="98" spans="1:29" s="7" customFormat="1" ht="380" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>999</v>
       </c>
@@ -16452,13 +16260,11 @@
       <c r="AB98" s="15">
         <v>525131</v>
       </c>
-      <c r="AC98" s="15"/>
-      <c r="AD98" s="15" t="s">
+      <c r="AC98" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="AE98" s="15"/>
     </row>
-    <row r="99" spans="1:31" s="7" customFormat="1" ht="409.5">
+    <row r="99" spans="1:29" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>1009</v>
       </c>
@@ -16540,13 +16346,11 @@
       <c r="AB99" s="15">
         <v>526040</v>
       </c>
-      <c r="AC99" s="15"/>
-      <c r="AD99" s="15" t="s">
+      <c r="AC99" s="15" t="s">
         <v>1018</v>
       </c>
-      <c r="AE99" s="15"/>
     </row>
-    <row r="100" spans="1:31" s="7" customFormat="1" ht="315">
+    <row r="100" spans="1:29" s="7" customFormat="1" ht="335" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>577</v>
       </c>
@@ -16628,215 +16432,13 @@
       <c r="AB100" s="15">
         <v>520010</v>
       </c>
-      <c r="AC100" s="15"/>
-      <c r="AD100" s="15" t="s">
+      <c r="AC100" s="15" t="s">
         <v>586</v>
       </c>
-      <c r="AE100" s="15"/>
     </row>
-    <row r="101" spans="1:31" s="7" customFormat="1"/>
-    <row r="102" spans="1:31" s="7" customFormat="1"/>
+    <row r="101" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="102" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="198">
-    <mergeCell ref="AD99:AE99"/>
-    <mergeCell ref="AD100:AE100"/>
-    <mergeCell ref="AD93:AE93"/>
-    <mergeCell ref="AD94:AE94"/>
-    <mergeCell ref="AD95:AE95"/>
-    <mergeCell ref="AD96:AE96"/>
-    <mergeCell ref="AD97:AE97"/>
-    <mergeCell ref="AD98:AE98"/>
-    <mergeCell ref="AD87:AE87"/>
-    <mergeCell ref="AD88:AE88"/>
-    <mergeCell ref="AD89:AE89"/>
-    <mergeCell ref="AD90:AE90"/>
-    <mergeCell ref="AD91:AE91"/>
-    <mergeCell ref="AD92:AE92"/>
-    <mergeCell ref="AD81:AE81"/>
-    <mergeCell ref="AD82:AE82"/>
-    <mergeCell ref="AD83:AE83"/>
-    <mergeCell ref="AD84:AE84"/>
-    <mergeCell ref="AD85:AE85"/>
-    <mergeCell ref="AD86:AE86"/>
-    <mergeCell ref="AD75:AE75"/>
-    <mergeCell ref="AD76:AE76"/>
-    <mergeCell ref="AD77:AE77"/>
-    <mergeCell ref="AD78:AE78"/>
-    <mergeCell ref="AD79:AE79"/>
-    <mergeCell ref="AD80:AE80"/>
-    <mergeCell ref="AD69:AE69"/>
-    <mergeCell ref="AD70:AE70"/>
-    <mergeCell ref="AD71:AE71"/>
-    <mergeCell ref="AD72:AE72"/>
-    <mergeCell ref="AD73:AE73"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="AD63:AE63"/>
-    <mergeCell ref="AD64:AE64"/>
-    <mergeCell ref="AD65:AE65"/>
-    <mergeCell ref="AD66:AE66"/>
-    <mergeCell ref="AD67:AE67"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="AD57:AE57"/>
-    <mergeCell ref="AD58:AE58"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AD60:AE60"/>
-    <mergeCell ref="AD61:AE61"/>
-    <mergeCell ref="AD62:AE62"/>
-    <mergeCell ref="AD51:AE51"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AD53:AE53"/>
-    <mergeCell ref="AD54:AE54"/>
-    <mergeCell ref="AD55:AE55"/>
-    <mergeCell ref="AD56:AE56"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="AD46:AE46"/>
-    <mergeCell ref="AD47:AE47"/>
-    <mergeCell ref="AD48:AE48"/>
-    <mergeCell ref="AD49:AE49"/>
-    <mergeCell ref="AD50:AE50"/>
-    <mergeCell ref="AD39:AE39"/>
-    <mergeCell ref="AD40:AE40"/>
-    <mergeCell ref="AD41:AE41"/>
-    <mergeCell ref="AD42:AE42"/>
-    <mergeCell ref="AD43:AE43"/>
-    <mergeCell ref="AD44:AE44"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="AD35:AE35"/>
-    <mergeCell ref="AD36:AE36"/>
-    <mergeCell ref="AD37:AE37"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AD28:AE28"/>
-    <mergeCell ref="AD29:AE29"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="AD15:AE15"/>
-    <mergeCell ref="AD16:AE16"/>
-    <mergeCell ref="AD17:AE17"/>
-    <mergeCell ref="AD18:AE18"/>
-    <mergeCell ref="AD19:AE19"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AD9:AE9"/>
-    <mergeCell ref="AD10:AE10"/>
-    <mergeCell ref="AD11:AE11"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AD14:AE14"/>
-    <mergeCell ref="AB98:AC98"/>
-    <mergeCell ref="AB99:AC99"/>
-    <mergeCell ref="AB100:AC100"/>
-    <mergeCell ref="AB94:AC94"/>
-    <mergeCell ref="AB95:AC95"/>
-    <mergeCell ref="AB96:AC96"/>
-    <mergeCell ref="AB97:AC97"/>
-    <mergeCell ref="AB77:AC77"/>
-    <mergeCell ref="AB78:AC78"/>
-    <mergeCell ref="AB79:AC79"/>
-    <mergeCell ref="AB68:AC68"/>
-    <mergeCell ref="AB69:AC69"/>
-    <mergeCell ref="AB70:AC70"/>
-    <mergeCell ref="AB71:AC71"/>
-    <mergeCell ref="AB72:AC72"/>
-    <mergeCell ref="AB73:AC73"/>
-    <mergeCell ref="AB62:AC62"/>
-    <mergeCell ref="AB63:AC63"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="AD8:AE8"/>
-    <mergeCell ref="AB92:AC92"/>
-    <mergeCell ref="AB93:AC93"/>
-    <mergeCell ref="AB86:AC86"/>
-    <mergeCell ref="AB87:AC87"/>
-    <mergeCell ref="AB88:AC88"/>
-    <mergeCell ref="AB89:AC89"/>
-    <mergeCell ref="AB90:AC90"/>
-    <mergeCell ref="AB91:AC91"/>
-    <mergeCell ref="AB80:AC80"/>
-    <mergeCell ref="AB81:AC81"/>
-    <mergeCell ref="AB82:AC82"/>
-    <mergeCell ref="AB83:AC83"/>
-    <mergeCell ref="AB84:AC84"/>
-    <mergeCell ref="AB85:AC85"/>
-    <mergeCell ref="AB74:AC74"/>
-    <mergeCell ref="AB75:AC75"/>
-    <mergeCell ref="AB76:AC76"/>
-    <mergeCell ref="AB64:AC64"/>
-    <mergeCell ref="AB65:AC65"/>
-    <mergeCell ref="AB66:AC66"/>
-    <mergeCell ref="AB67:AC67"/>
-    <mergeCell ref="AB56:AC56"/>
-    <mergeCell ref="AB57:AC57"/>
-    <mergeCell ref="AB58:AC58"/>
-    <mergeCell ref="AB59:AC59"/>
-    <mergeCell ref="AB60:AC60"/>
-    <mergeCell ref="AB61:AC61"/>
-    <mergeCell ref="AB50:AC50"/>
-    <mergeCell ref="AB51:AC51"/>
-    <mergeCell ref="AB52:AC52"/>
-    <mergeCell ref="AB53:AC53"/>
-    <mergeCell ref="AB54:AC54"/>
-    <mergeCell ref="AB55:AC55"/>
-    <mergeCell ref="AB44:AC44"/>
-    <mergeCell ref="AB45:AC45"/>
-    <mergeCell ref="AB46:AC46"/>
-    <mergeCell ref="AB47:AC47"/>
-    <mergeCell ref="AB48:AC48"/>
-    <mergeCell ref="AB49:AC49"/>
-    <mergeCell ref="AB38:AC38"/>
-    <mergeCell ref="AB39:AC39"/>
-    <mergeCell ref="AB40:AC40"/>
-    <mergeCell ref="AB41:AC41"/>
-    <mergeCell ref="AB42:AC42"/>
-    <mergeCell ref="AB43:AC43"/>
-    <mergeCell ref="AB32:AC32"/>
-    <mergeCell ref="AB33:AC33"/>
-    <mergeCell ref="AB34:AC34"/>
-    <mergeCell ref="AB35:AC35"/>
-    <mergeCell ref="AB36:AC36"/>
-    <mergeCell ref="AB37:AC37"/>
-    <mergeCell ref="AB26:AC26"/>
-    <mergeCell ref="AB27:AC27"/>
-    <mergeCell ref="AB28:AC28"/>
-    <mergeCell ref="AB29:AC29"/>
-    <mergeCell ref="AB30:AC30"/>
-    <mergeCell ref="AB31:AC31"/>
-    <mergeCell ref="AB20:AC20"/>
-    <mergeCell ref="AB21:AC21"/>
-    <mergeCell ref="AB22:AC22"/>
-    <mergeCell ref="AB23:AC23"/>
-    <mergeCell ref="AB24:AC24"/>
-    <mergeCell ref="AB25:AC25"/>
-    <mergeCell ref="AB17:AC17"/>
-    <mergeCell ref="AB18:AC18"/>
-    <mergeCell ref="AB19:AC19"/>
-    <mergeCell ref="AB8:AC8"/>
-    <mergeCell ref="AB9:AC9"/>
-    <mergeCell ref="AB10:AC10"/>
-    <mergeCell ref="AB11:AC11"/>
-    <mergeCell ref="AB12:AC12"/>
-    <mergeCell ref="AB13:AC13"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AB5:AC5"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AB7:AC7"/>
-    <mergeCell ref="AB14:AC14"/>
-    <mergeCell ref="AB15:AC15"/>
-    <mergeCell ref="AB16:AC16"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="J3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
